--- a/cad/amr07/BOM.xlsx
+++ b/cad/amr07/BOM.xlsx
@@ -22,9 +22,9 @@
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Area" vbProcedure="false">未選定!$A$1:$F$24</definedName>
     <definedName function="false" hidden="false" localSheetId="4" name="_xlnm.Print_Titles" vbProcedure="false">未選定!$1:$4</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">未選定!$A$4:$F$24</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">概要!$A$1:$C$16</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">概要!$A$1:$C$17</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">概要!$1:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">概要!$A$4:$C$16</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">概要!$A$4:$C$17</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">締結部品!$A$1:$F$19</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">締結部品!$1:$4</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">締結部品!$A$4:$F$19</definedName>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="796">
   <si>
     <t xml:space="preserve">AMR-01 / A6　調達BOM</t>
   </si>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">円の途中小計</t>
   </si>
   <si>
-    <t xml:space="preserve">販売記録・参考価格・仮枠・材料消費を含む。未見積は含まない。</t>
+    <t xml:space="preserve">キャスターをナフコ店舗受取498円＋送料0円とする条件。受取店・在庫未確定。販売記録・仮枠・材料消費を含む。</t>
   </si>
   <si>
     <t xml:space="preserve">USDの途中小計</t>
@@ -153,6 +153,15 @@
   </si>
   <si>
     <t xml:space="preserve">自律移動用センサー・上位計算機一式まで価格確定したBOMではない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">格子穴上板のCNC比較見積</t>
+  </si>
+  <si>
+    <t xml:space="preserve">別資料、現行BOMには未加算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300×300×4、50mmピッチ36穴。CNC品を採用する場合は板素材代と対象送料を置換し、重複加算しない。</t>
   </si>
   <si>
     <t xml:space="preserve">購入品・材料・送料</t>
@@ -310,12 +319,12 @@
     <t xml:space="preserve">1個×1</t>
   </si>
   <si>
-    <t xml:space="preserve">過去価格の引継ぎ
-型式選定済</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タナカ金物
-キャスター構成部5形状を完成品1個として購入。送料S02。</t>
+    <t xml:space="preserve">販売表示・条件付き
+型式維持・個人購入の店舗受取を第一候補</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ナフコ（店舗受取）
+完成品1個。税込498円＋店舗受取送料0円。受取店/在庫未確定、交通費別。ナフコ包装JANは2100256559029、受入時に420G-R50/高さ65/穴ピッチ46×35を照合。</t>
   </si>
   <si>
     <t xml:space="preserve">P01</t>
@@ -677,14 +686,12 @@
     <t xml:space="preserve">送料／諸費1式</t>
   </si>
   <si>
-    <t xml:space="preserve">過去価格の引継ぎ
-参考・条件付き</t>
-  </si>
-  <si>
-    <t xml:space="preserve">タナカ金物</t>
-  </si>
-  <si>
-    <t xml:space="preserve">本州・4900円未満という旧確認条件。配送先で確定。</t>
+    <t xml:space="preserve">販売表示・条件付き
+店舗受取の場合のみ0円</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ナフコ（店舗受取）
+商品ページの店舗受取送料無料条件。自宅配送費ではない。受取店・準備日は注文前に確認。</t>
   </si>
   <si>
     <t xml:space="preserve">S03</t>
@@ -2954,8 +2961,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BOMTable1" displayName="BOMTable1" ref="A4:C16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A4:C16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="BOMTable1" displayName="BOMTable1" ref="A4:C17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A4:C17"/>
   <tableColumns count="3">
     <tableColumn id="1" name="項目"/>
     <tableColumn id="2" name="値"/>
@@ -3220,7 +3227,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29"/>
@@ -3259,7 +3266,7 @@
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">SUMIF(購入品!H5:H44,"JPY",購入品!G5:G44)</f>
-        <v>54939</v>
+        <v>54414</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>6</v>
@@ -3387,8 +3394,19 @@
         <v>35</v>
       </c>
     </row>
+    <row r="17" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:C16"/>
+  <autoFilter ref="A4:C17"/>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
@@ -3430,7 +3448,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3445,7 +3463,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3460,51 +3478,51 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>1</v>
@@ -3517,30 +3535,30 @@
         <v>1952</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>1</v>
@@ -3553,30 +3571,30 @@
         <v>1467</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J6" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>8</v>
@@ -3589,30 +3607,30 @@
         <v>1540</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="21"/>
@@ -3620,30 +3638,30 @@
         <v>1200</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J8" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E9" s="13"/>
       <c r="F9" s="23"/>
@@ -3651,66 +3669,66 @@
         <v>500</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>10</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>1</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>373</v>
+        <v>498</v>
       </c>
       <c r="G10" s="19" t="n">
         <f aca="false">E10*F10</f>
-        <v>373</v>
+        <v>498</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E11" s="13"/>
       <c r="F11" s="23"/>
@@ -3718,30 +3736,30 @@
         <v>900</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>10</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>2</v>
@@ -3754,30 +3772,30 @@
         <v>14000</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>2</v>
@@ -3790,30 +3808,30 @@
         <v>9240</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E14" s="17" t="n">
         <v>1</v>
@@ -3826,30 +3844,30 @@
         <v>75.02</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>1</v>
@@ -3862,30 +3880,30 @@
         <v>4521</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E16" s="17" t="n">
         <v>1</v>
@@ -3898,30 +3916,30 @@
         <v>1507</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>2</v>
@@ -3934,30 +3952,30 @@
         <v>786</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J17" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E18" s="17"/>
       <c r="F18" s="21"/>
@@ -3965,30 +3983,30 @@
         <v>1500</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E19" s="13"/>
       <c r="F19" s="23"/>
@@ -3996,30 +4014,30 @@
         <v>300</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>0</v>
@@ -4029,30 +4047,30 @@
         <v>600</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E21" s="13"/>
       <c r="F21" s="23"/>
@@ -4060,30 +4078,30 @@
         <v>500</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>10</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E22" s="17"/>
       <c r="F22" s="21"/>
@@ -4091,30 +4109,30 @@
         <v>2300</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="J22" s="6" t="s">
         <v>10</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>1</v>
@@ -4127,30 +4145,30 @@
         <v>319</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E24" s="17"/>
       <c r="F24" s="21"/>
@@ -4158,30 +4176,30 @@
         <v>500</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J24" s="6" t="s">
         <v>10</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>1</v>
@@ -4194,30 +4212,30 @@
         <v>3298</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E26" s="17" t="n">
         <v>2</v>
@@ -4230,30 +4248,30 @@
         <v>770</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>1</v>
@@ -4266,30 +4284,30 @@
         <v>920</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E28" s="17" t="n">
         <v>1</v>
@@ -4302,30 +4320,30 @@
         <v>140</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J28" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>1</v>
@@ -4338,30 +4356,30 @@
         <v>33</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J29" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>1</v>
@@ -4374,30 +4392,30 @@
         <v>850</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J30" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>1</v>
@@ -4410,30 +4428,30 @@
         <v>70</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J31" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E32" s="17" t="n">
         <v>1</v>
@@ -4446,30 +4464,30 @@
         <v>1033</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J32" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>1</v>
@@ -4482,30 +4500,30 @@
         <v>30</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J33" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E34" s="17" t="n">
         <v>1</v>
@@ -4518,30 +4536,30 @@
         <v>20</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J34" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>1</v>
@@ -4554,30 +4572,30 @@
         <v>100</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J35" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>1</v>
@@ -4590,30 +4608,30 @@
         <v>20</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J36" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>1</v>
@@ -4626,61 +4644,61 @@
         <v>300</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J37" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E38" s="17"/>
       <c r="F38" s="21"/>
       <c r="G38" s="19" t="n">
-        <v>650</v>
+        <v>0</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
+      </c>
+      <c r="J38" s="20" t="s">
+        <v>58</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E39" s="13"/>
       <c r="F39" s="23"/>
@@ -4688,30 +4706,30 @@
         <v>1000</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E40" s="17"/>
       <c r="F40" s="21"/>
@@ -4719,30 +4737,30 @@
         <v>500</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J40" s="6" t="s">
         <v>10</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E41" s="13"/>
       <c r="F41" s="23"/>
@@ -4750,59 +4768,59 @@
         <v>0</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J41" s="16" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E42" s="17"/>
       <c r="F42" s="21"/>
       <c r="G42" s="22"/>
       <c r="H42" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E43" s="13"/>
       <c r="F43" s="23"/>
@@ -4810,30 +4828,30 @@
         <v>1200</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E44" s="17"/>
       <c r="F44" s="21"/>
@@ -4841,16 +4859,16 @@
         <v>7.23</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J44" s="20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -4890,8 +4908,9 @@
     <hyperlink ref="J35" r:id="rId22" display="参照を開く"/>
     <hyperlink ref="J36" r:id="rId23" display="参照を開く"/>
     <hyperlink ref="J37" r:id="rId24" display="参照を開く"/>
-    <hyperlink ref="J41" r:id="rId25" display="参照を開く"/>
-    <hyperlink ref="J44" r:id="rId26" display="参照を開く"/>
+    <hyperlink ref="J38" r:id="rId25" display="参照を開く"/>
+    <hyperlink ref="J41" r:id="rId26" display="参照を開く"/>
+    <hyperlink ref="J44" r:id="rId27" display="参照を開く"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.511811023622047" footer="0.5"/>
@@ -4900,9 +4919,9 @@
     <oddHeader/>
     <oddFooter>&amp;CAMR-01 A6 | &amp;P / &amp;N</oddFooter>
   </headerFooter>
-  <drawing r:id="rId27"/>
+  <drawing r:id="rId28"/>
   <tableParts>
-    <tablePart r:id="rId28"/>
+    <tablePart r:id="rId29"/>
   </tableParts>
 </worksheet>
 </file>
@@ -4924,7 +4943,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4934,7 +4953,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4944,27 +4963,27 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B5" s="25" t="n">
         <v>6</v>
@@ -4976,15 +4995,15 @@
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B6" s="26" t="n">
         <v>50</v>
@@ -4996,15 +5015,15 @@
         <v>34</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B7" s="25" t="n">
         <v>6</v>
@@ -5016,15 +5035,15 @@
         <v>6</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B8" s="26" t="n">
         <v>8</v>
@@ -5036,15 +5055,15 @@
         <v>8</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B9" s="25" t="n">
         <v>8</v>
@@ -5056,15 +5075,15 @@
         <v>8</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B10" s="26" t="n">
         <v>8</v>
@@ -5076,15 +5095,15 @@
         <v>8</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B11" s="25" t="n">
         <v>12</v>
@@ -5096,15 +5115,15 @@
         <v>12</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B12" s="26" t="n">
         <v>12</v>
@@ -5116,15 +5135,15 @@
         <v>12</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B13" s="25" t="n">
         <v>4</v>
@@ -5136,15 +5155,15 @@
         <v>4</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B14" s="26" t="n">
         <v>12</v>
@@ -5156,15 +5175,15 @@
         <v>12</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B15" s="25" t="n">
         <v>8</v>
@@ -5176,15 +5195,15 @@
         <v>8</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B16" s="26" t="n">
         <v>36</v>
@@ -5196,15 +5215,15 @@
         <v>20</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B17" s="25" t="n">
         <v>4</v>
@@ -5216,15 +5235,15 @@
         <v>4</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B18" s="26" t="n">
         <v>6</v>
@@ -5236,15 +5255,15 @@
         <v>6</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B19" s="25" t="n">
         <v>6</v>
@@ -5256,10 +5275,10 @@
         <v>0</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -5302,7 +5321,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5314,7 +5333,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5326,262 +5345,262 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>2</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C6" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C7" s="25" t="n">
         <v>4</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C8" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C9" s="25" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C10" s="26" t="n">
         <v>4</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C12" s="26" t="n">
         <v>1</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C13" s="25" t="n">
         <v>1</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -5633,7 +5652,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5643,7 +5662,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5653,422 +5672,422 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>307</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -6108,7 +6127,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6117,7 +6136,7 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6126,2040 +6145,2040 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>403</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>401</v>
       </c>
       <c r="E6" s="6"/>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E9" s="4"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E11" s="4"/>
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E16" s="6"/>
     </row>
     <row r="17" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="4" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E21" s="4"/>
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E26" s="6"/>
     </row>
     <row r="27" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E31" s="4"/>
     </row>
     <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E38" s="6"/>
     </row>
     <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="4" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E45" s="4"/>
     </row>
     <row r="46" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="4" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E50" s="6"/>
     </row>
     <row r="51" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="4" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E72" s="6"/>
     </row>
     <row r="73" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="4" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="4" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="4" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="4" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="4" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="4" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="4" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E87" s="4"/>
     </row>
     <row r="88" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C88" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="D88" s="6" t="s">
         <v>569</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>567</v>
       </c>
       <c r="E88" s="6"/>
     </row>
     <row r="89" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="4" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E89" s="4"/>
     </row>
     <row r="90" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E90" s="6"/>
     </row>
     <row r="91" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="4" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E98" s="6"/>
     </row>
     <row r="99" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E99" s="4"/>
     </row>
     <row r="100" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E100" s="6"/>
     </row>
     <row r="101" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="4" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E101" s="4"/>
     </row>
     <row r="102" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="4" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="4" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="4" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="4" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="4" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="4" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E114" s="6"/>
     </row>
     <row r="115" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="4" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="4" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="4" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="4" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="4" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E123" s="4"/>
     </row>
     <row r="124" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E124" s="6"/>
     </row>
     <row r="125" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="4" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E125" s="4"/>
     </row>
     <row r="126" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E126" s="6"/>
     </row>
     <row r="127" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>30</v>
@@ -8168,217 +8187,217 @@
     </row>
     <row r="128" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="6" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="4" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="6" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="4" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="6" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="4" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="6" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="4" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E139" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="6" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>30</v>
@@ -8387,217 +8406,217 @@
     </row>
     <row r="141" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="4" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="6" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="4" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="6" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="4" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="6" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="4" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="4" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="6" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="6" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="4" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>30</v>
@@ -8606,1229 +8625,1229 @@
     </row>
     <row r="154" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="6" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="4" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="6" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="4" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="6" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="4" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="6" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="6" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="4" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="6" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D164" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="4" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="6" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="4" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D168" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="4" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="6" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="4" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E171" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="6" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D172" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E172" s="6"/>
     </row>
     <row r="173" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="4" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E173" s="4"/>
     </row>
     <row r="174" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="6" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E174" s="6"/>
     </row>
     <row r="175" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="4" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E175" s="4"/>
     </row>
     <row r="176" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="6" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D176" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E176" s="6"/>
     </row>
     <row r="177" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="4" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E177" s="4"/>
     </row>
     <row r="178" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="6" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D178" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E178" s="6"/>
     </row>
     <row r="179" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="6" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D180" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="6" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D182" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="6" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="6" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="4" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="6" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="189" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="4" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="6" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="4" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="6" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="4" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="194" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="6" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="4" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="6" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="4" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="6" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="4" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="6" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D200" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="4" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="6" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="4" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="6" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="D204" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="4" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="6" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="4" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="6" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="4" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="210" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="6" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="4" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="6" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="4" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="6" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="4" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E215" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="216" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="4" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E217" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="6" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="4" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E219" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="6" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="4" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E221" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="6" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="4" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="6" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E225" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="6" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E226" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/cad/amr07/BOM.xlsx
+++ b/cad/amr07/BOM.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="796">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="800">
   <si>
     <t xml:space="preserve">AMR-01 / A6　調達BOM</t>
   </si>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">円の途中小計</t>
   </si>
   <si>
-    <t xml:space="preserve">キャスターをナフコ店舗受取498円＋送料0円とする条件。受取店・在庫未確定。販売記録・仮枠・材料消費を含む。</t>
+    <t xml:space="preserve">キャスターをAmazon273円＋既存Prime会員条件の送料0円とする条件。会員ログイン後の最終注文額は未確認。販売記録・仮枠・材料消費を含む。</t>
   </si>
   <si>
     <t xml:space="preserve">USDの途中小計</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">タイヤ・キャスター・座金・タイヤ送料を再確認</t>
   </si>
   <si>
-    <t xml:space="preserve">Amazonは再取得できず既存価格。その他は2026-09-21等の既存記録・仮枠。</t>
+    <t xml:space="preserve">フレームのAmazon価格は再取得できず既存価格。キャスターはAmazon販売発送273円を確認。その他は既存記録・仮枠。</t>
   </si>
   <si>
     <t xml:space="preserve">使用数と購入数</t>
@@ -310,7 +310,7 @@
   </si>
   <si>
     <t xml:space="preserve">自在キャスター
-ハンマー420G-R50、径50・取付高65mm</t>
+TRUSCO TYG-50、径50・取付高65mm、穴ピッチ46×35</t>
   </si>
   <si>
     <t xml:space="preserve">1個</t>
@@ -320,11 +320,11 @@
   </si>
   <si>
     <t xml:space="preserve">販売表示・条件付き
-型式維持・個人購入の店舗受取を第一候補</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ナフコ（店舗受取）
-完成品1個。税込498円＋店舗受取送料0円。受取店/在庫未確定、交通費別。ナフコ包装JANは2100256559029、受入時に420G-R50/高さ65/穴ピッチ46×35を照合。</t>
+Amazon販売発送を確認・Prime会員条件の第一候補</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon.co.jp（販売・発送）
+完成品1個、税込273円。Amazon.co.jp販売・発送の出品。既存Prime会員の対象配送を条件に送料0円（公式配送規定）。会員としての最終注文画面は未確認。JAN4989999424980、公称高さ65mm・穴46×35を受入照合。</t>
   </si>
   <si>
     <t xml:space="preserve">P01</t>
@@ -687,11 +687,11 @@
   </si>
   <si>
     <t xml:space="preserve">販売表示・条件付き
-店舗受取の場合のみ0円</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ナフコ（店舗受取）
-商品ページの店舗受取送料無料条件。自宅配送費ではない。受取店・準備日は注文前に確認。</t>
+既存Prime会員の対象配送条件で0円</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon.co.jp（Prime会員条件）
+Amazon公式の会員配送規定を適用する条件。会員ログイン後の最終注文額ではない。非会員の単品購入は別送料。新規会費は含めない。コーナン店舗受取なら商品283円＋受取送料0円。</t>
   </si>
   <si>
     <t xml:space="preserve">S03</t>
@@ -1990,7 +1990,7 @@
     <t xml:space="preserve">CasterTop</t>
   </si>
   <si>
-    <t xml:space="preserve">Hammer420G-R50 | unchanged</t>
+    <t xml:space="preserve">TRUSCO TYG-50 | CasterTop | nominal proxy</t>
   </si>
   <si>
     <t xml:space="preserve">CasterBolt_0</t>
@@ -2044,13 +2044,25 @@
     <t xml:space="preserve">SwivelRace</t>
   </si>
   <si>
+    <t xml:space="preserve">TRUSCO TYG-50 | SwivelRace | nominal proxy</t>
+  </si>
+  <si>
     <t xml:space="preserve">CasterFork</t>
   </si>
   <si>
+    <t xml:space="preserve">TRUSCO TYG-50 | CasterFork | nominal proxy</t>
+  </si>
+  <si>
     <t xml:space="preserve">CasterTire</t>
   </si>
   <si>
+    <t xml:space="preserve">TRUSCO TYG-50 | CasterTire | nominal proxy</t>
+  </si>
+  <si>
     <t xml:space="preserve">CasterCore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUSCO TYG-50 | CasterCore | nominal proxy</t>
   </si>
   <si>
     <t xml:space="preserve">BatteryCradlePLA</t>
@@ -3266,7 +3278,7 @@
       </c>
       <c r="B5" s="5" t="n">
         <f aca="false">SUMIF(購入品!H5:H44,"JPY",購入品!G5:G44)</f>
-        <v>54414</v>
+        <v>54189</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>6</v>
@@ -3311,7 +3323,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="10" t="n">
-        <v>8.73314316476638</v>
+        <v>8.74814316476638</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>16</v>
@@ -3698,11 +3710,11 @@
         <v>1</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>498</v>
+        <v>273</v>
       </c>
       <c r="G10" s="19" t="n">
         <f aca="false">E10*F10</f>
-        <v>498</v>
+        <v>273</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>56</v>
@@ -8118,7 +8130,7 @@
         <v>82</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>569</v>
@@ -8127,13 +8139,13 @@
     </row>
     <row r="124" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>82</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>569</v>
@@ -8142,13 +8154,13 @@
     </row>
     <row r="125" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="4" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B125" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>569</v>
@@ -8157,13 +8169,13 @@
     </row>
     <row r="126" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>82</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="D126" s="6" t="s">
         <v>569</v>
@@ -8172,13 +8184,13 @@
     </row>
     <row r="127" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="4" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="B127" s="4" t="s">
         <v>137</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>30</v>
@@ -8187,13 +8199,13 @@
     </row>
     <row r="128" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="D128" s="6" t="s">
         <v>418</v>
@@ -8204,13 +8216,13 @@
     </row>
     <row r="129" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B129" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>418</v>
@@ -8221,13 +8233,13 @@
     </row>
     <row r="130" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="6" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>418</v>
@@ -8238,13 +8250,13 @@
     </row>
     <row r="131" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="B131" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>418</v>
@@ -8255,13 +8267,13 @@
     </row>
     <row r="132" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>418</v>
@@ -8272,13 +8284,13 @@
     </row>
     <row r="133" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="4" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="B133" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>418</v>
@@ -8289,13 +8301,13 @@
     </row>
     <row r="134" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="6" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>418</v>
@@ -8306,13 +8318,13 @@
     </row>
     <row r="135" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="4" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B135" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="D135" s="4" t="s">
         <v>418</v>
@@ -8323,13 +8335,13 @@
     </row>
     <row r="136" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="6" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>418</v>
@@ -8340,13 +8352,13 @@
     </row>
     <row r="137" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="4" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B137" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>418</v>
@@ -8357,13 +8369,13 @@
     </row>
     <row r="138" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="6" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>418</v>
@@ -8374,13 +8386,13 @@
     </row>
     <row r="139" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="4" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B139" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>418</v>
@@ -8391,13 +8403,13 @@
     </row>
     <row r="140" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="6" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>137</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>30</v>
@@ -8406,13 +8418,13 @@
     </row>
     <row r="141" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="4" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="B141" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>418</v>
@@ -8423,13 +8435,13 @@
     </row>
     <row r="142" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="6" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>418</v>
@@ -8440,13 +8452,13 @@
     </row>
     <row r="143" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="4" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B143" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>418</v>
@@ -8457,13 +8469,13 @@
     </row>
     <row r="144" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="6" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>418</v>
@@ -8474,13 +8486,13 @@
     </row>
     <row r="145" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="4" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="B145" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>418</v>
@@ -8491,13 +8503,13 @@
     </row>
     <row r="146" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="6" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="D146" s="6" t="s">
         <v>418</v>
@@ -8508,13 +8520,13 @@
     </row>
     <row r="147" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="4" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="B147" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>418</v>
@@ -8525,13 +8537,13 @@
     </row>
     <row r="148" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>418</v>
@@ -8542,13 +8554,13 @@
     </row>
     <row r="149" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="4" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="B149" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>418</v>
@@ -8559,13 +8571,13 @@
     </row>
     <row r="150" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="6" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>418</v>
@@ -8576,13 +8588,13 @@
     </row>
     <row r="151" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="4" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="B151" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>418</v>
@@ -8593,13 +8605,13 @@
     </row>
     <row r="152" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="6" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>418</v>
@@ -8610,13 +8622,13 @@
     </row>
     <row r="153" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="4" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="B153" s="4" t="s">
         <v>137</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>30</v>
@@ -8625,13 +8637,13 @@
     </row>
     <row r="154" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="6" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>418</v>
@@ -8642,13 +8654,13 @@
     </row>
     <row r="155" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="4" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="B155" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>418</v>
@@ -8659,13 +8671,13 @@
     </row>
     <row r="156" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="6" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>418</v>
@@ -8676,13 +8688,13 @@
     </row>
     <row r="157" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="4" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="B157" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>418</v>
@@ -8693,13 +8705,13 @@
     </row>
     <row r="158" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="6" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>418</v>
@@ -8710,13 +8722,13 @@
     </row>
     <row r="159" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="4" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B159" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>418</v>
@@ -8727,13 +8739,13 @@
     </row>
     <row r="160" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="6" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>418</v>
@@ -8744,13 +8756,13 @@
     </row>
     <row r="161" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="4" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="B161" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>418</v>
@@ -8761,13 +8773,13 @@
     </row>
     <row r="162" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="6" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>70</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>418</v>
@@ -8778,13 +8790,13 @@
     </row>
     <row r="163" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="4" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="B163" s="4" t="s">
         <v>148</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>418</v>
@@ -8795,13 +8807,13 @@
     </row>
     <row r="164" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="6" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>148</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>418</v>
@@ -8812,13 +8824,13 @@
     </row>
     <row r="165" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="4" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B165" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>418</v>
@@ -8829,13 +8841,13 @@
     </row>
     <row r="166" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="6" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>151</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>418</v>
@@ -8846,13 +8858,13 @@
     </row>
     <row r="167" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="4" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="B167" s="4" t="s">
         <v>151</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>418</v>
@@ -8863,13 +8875,13 @@
     </row>
     <row r="168" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="6" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>151</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>418</v>
@@ -8880,13 +8892,13 @@
     </row>
     <row r="169" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="4" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B169" s="4" t="s">
         <v>151</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>418</v>
@@ -8897,13 +8909,13 @@
     </row>
     <row r="170" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="6" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>151</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="D170" s="6" t="s">
         <v>418</v>
@@ -8914,13 +8926,13 @@
     </row>
     <row r="171" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="4" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B171" s="4" t="s">
         <v>151</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>418</v>
@@ -8931,13 +8943,13 @@
     </row>
     <row r="172" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="6" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>111</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="D172" s="6" t="s">
         <v>403</v>
@@ -8946,13 +8958,13 @@
     </row>
     <row r="173" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="4" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="B173" s="4" t="s">
         <v>116</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>403</v>
@@ -8961,13 +8973,13 @@
     </row>
     <row r="174" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="6" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>116</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="D174" s="6" t="s">
         <v>403</v>
@@ -8976,13 +8988,13 @@
     </row>
     <row r="175" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="4" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="B175" s="4" t="s">
         <v>116</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>403</v>
@@ -8991,13 +9003,13 @@
     </row>
     <row r="176" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="6" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>116</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="D176" s="6" t="s">
         <v>403</v>
@@ -9006,13 +9018,13 @@
     </row>
     <row r="177" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="4" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="B177" s="4" t="s">
         <v>116</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>403</v>
@@ -9021,13 +9033,13 @@
     </row>
     <row r="178" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="6" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>116</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="D178" s="6" t="s">
         <v>403</v>
@@ -9036,13 +9048,13 @@
     </row>
     <row r="179" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="4" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="B179" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>418</v>
@@ -9053,13 +9065,13 @@
     </row>
     <row r="180" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="6" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D180" s="6" t="s">
         <v>418</v>
@@ -9070,13 +9082,13 @@
     </row>
     <row r="181" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="4" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B181" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>418</v>
@@ -9087,13 +9099,13 @@
     </row>
     <row r="182" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="6" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>418</v>
@@ -9104,13 +9116,13 @@
     </row>
     <row r="183" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="4" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="B183" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>418</v>
@@ -9121,13 +9133,13 @@
     </row>
     <row r="184" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="6" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>418</v>
@@ -9138,13 +9150,13 @@
     </row>
     <row r="185" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="4" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="B185" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>418</v>
@@ -9155,13 +9167,13 @@
     </row>
     <row r="186" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="6" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B186" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>418</v>
@@ -9172,13 +9184,13 @@
     </row>
     <row r="187" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="4" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>418</v>
@@ -9189,13 +9201,13 @@
     </row>
     <row r="188" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="6" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>418</v>
@@ -9206,13 +9218,13 @@
     </row>
     <row r="189" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="4" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="B189" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>418</v>
@@ -9223,13 +9235,13 @@
     </row>
     <row r="190" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="6" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="D190" s="6" t="s">
         <v>418</v>
@@ -9240,13 +9252,13 @@
     </row>
     <row r="191" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="4" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="B191" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>418</v>
@@ -9257,13 +9269,13 @@
     </row>
     <row r="192" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="6" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="D192" s="6" t="s">
         <v>418</v>
@@ -9274,13 +9286,13 @@
     </row>
     <row r="193" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="4" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B193" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>418</v>
@@ -9291,13 +9303,13 @@
     </row>
     <row r="194" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="6" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="D194" s="6" t="s">
         <v>418</v>
@@ -9308,13 +9320,13 @@
     </row>
     <row r="195" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="4" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B195" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>418</v>
@@ -9325,13 +9337,13 @@
     </row>
     <row r="196" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="6" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="D196" s="6" t="s">
         <v>418</v>
@@ -9342,13 +9354,13 @@
     </row>
     <row r="197" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="4" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="B197" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="D197" s="4" t="s">
         <v>418</v>
@@ -9359,13 +9371,13 @@
     </row>
     <row r="198" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="6" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="D198" s="6" t="s">
         <v>418</v>
@@ -9376,13 +9388,13 @@
     </row>
     <row r="199" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="4" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="B199" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="D199" s="4" t="s">
         <v>418</v>
@@ -9393,13 +9405,13 @@
     </row>
     <row r="200" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="6" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="D200" s="6" t="s">
         <v>418</v>
@@ -9410,13 +9422,13 @@
     </row>
     <row r="201" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="4" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="B201" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="D201" s="4" t="s">
         <v>418</v>
@@ -9427,13 +9439,13 @@
     </row>
     <row r="202" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="6" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="D202" s="6" t="s">
         <v>418</v>
@@ -9444,13 +9456,13 @@
     </row>
     <row r="203" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="4" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="B203" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>418</v>
@@ -9461,13 +9473,13 @@
     </row>
     <row r="204" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="6" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="B204" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="D204" s="6" t="s">
         <v>418</v>
@@ -9478,13 +9490,13 @@
     </row>
     <row r="205" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="4" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="B205" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="D205" s="4" t="s">
         <v>418</v>
@@ -9495,13 +9507,13 @@
     </row>
     <row r="206" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="6" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="D206" s="6" t="s">
         <v>418</v>
@@ -9512,13 +9524,13 @@
     </row>
     <row r="207" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="4" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B207" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="D207" s="4" t="s">
         <v>418</v>
@@ -9529,13 +9541,13 @@
     </row>
     <row r="208" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="6" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="D208" s="6" t="s">
         <v>418</v>
@@ -9546,13 +9558,13 @@
     </row>
     <row r="209" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="4" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B209" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="D209" s="4" t="s">
         <v>418</v>
@@ -9563,13 +9575,13 @@
     </row>
     <row r="210" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="6" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D210" s="6" t="s">
         <v>418</v>
@@ -9580,13 +9592,13 @@
     </row>
     <row r="211" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="4" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B211" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="D211" s="4" t="s">
         <v>418</v>
@@ -9597,13 +9609,13 @@
     </row>
     <row r="212" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="6" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="D212" s="6" t="s">
         <v>418</v>
@@ -9614,13 +9626,13 @@
     </row>
     <row r="213" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="4" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="B213" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="D213" s="4" t="s">
         <v>418</v>
@@ -9631,13 +9643,13 @@
     </row>
     <row r="214" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="6" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B214" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="D214" s="6" t="s">
         <v>418</v>
@@ -9648,13 +9660,13 @@
     </row>
     <row r="215" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="4" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="B215" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="D215" s="4" t="s">
         <v>418</v>
@@ -9665,13 +9677,13 @@
     </row>
     <row r="216" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="6" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="B216" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="D216" s="6" t="s">
         <v>418</v>
@@ -9682,13 +9694,13 @@
     </row>
     <row r="217" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="4" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="B217" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="D217" s="4" t="s">
         <v>418</v>
@@ -9699,13 +9711,13 @@
     </row>
     <row r="218" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="6" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="B218" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="D218" s="6" t="s">
         <v>418</v>
@@ -9716,13 +9728,13 @@
     </row>
     <row r="219" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="4" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="B219" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="D219" s="4" t="s">
         <v>418</v>
@@ -9733,13 +9745,13 @@
     </row>
     <row r="220" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="6" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="D220" s="6" t="s">
         <v>418</v>
@@ -9750,13 +9762,13 @@
     </row>
     <row r="221" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="4" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="B221" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="D221" s="4" t="s">
         <v>418</v>
@@ -9767,13 +9779,13 @@
     </row>
     <row r="222" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="6" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C222" s="6" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D222" s="6" t="s">
         <v>418</v>
@@ -9784,13 +9796,13 @@
     </row>
     <row r="223" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="4" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B223" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="D223" s="4" t="s">
         <v>418</v>
@@ -9801,13 +9813,13 @@
     </row>
     <row r="224" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="6" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="B224" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D224" s="6" t="s">
         <v>418</v>
@@ -9818,13 +9830,13 @@
     </row>
     <row r="225" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="4" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="B225" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="D225" s="4" t="s">
         <v>418</v>
@@ -9835,13 +9847,13 @@
     </row>
     <row r="226" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="6" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>126</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="D226" s="6" t="s">
         <v>418</v>
